--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/farris.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/farris.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Alguém...</t>
+          <t>Tem... tem... alguém...</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Uh... Uh... Alguém... Tem alguém aí?</t>
+          <t>Tem... tem... alguém... tem alguém aí?</t>
         </is>
       </c>
     </row>
@@ -660,8 +660,8 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Oh... Agradeço à misericordiosa Ehekatl por este encontro.
-Eu sou Farris, o contador de histórias de Olvina. Algo incomum está acontecendo em Nymelle, e vim a esta caverna com um grupo de mercenários. Mas, infelizmente, fomos atacados por monstros ferozes.</t>
+          <t>Oh... graças à bondosa Ehekatl por este encontro.
+Sou Farris, a contadora de histórias de Olvina. Algo incomum anda acontecendo em Nymelle e vim a esta caverna com um grupo de espadachins contratados. Mas, ai de mim, fomos atacados por monstros ferozes.</t>
         </is>
       </c>
     </row>
@@ -697,9 +697,8 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Como recitador das tradições de Mysilia, preciso saber o que está acontecendo nesta terra. No entanto, com meu grupo perdido, não tenho escolha a não ser recuar..._x000D_
-_x000D_
-Se desejar seguir em frente, eu lhe darei a chave desta passagem. Por favor, vá e descubra o que está acontecendo nas profundezas de Nymelle.</t>
+          <t>Preciso saber o que se passa nesta terra, como recitante das tradições de Mysilia. Com meu grupo perdido, porém, não me resta alternativa senão voltar...
+Vou te dar a chave desta passagem, se quiser seguir. Por favor, vá ver o que está acontecendo no fundo de Nymelle.</t>
         </is>
       </c>
     </row>
@@ -723,11 +722,9 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Oh... seu acampamento não fica longe daqui?_x000D_
-_x000D_
-Então irei para lá e aguardarei suas notícias. Procure-me quando terminar sua busca, tenho algo que preciso lhe contar._x000D_
-_x000D_
-Bem então, aventureiro, desejo que retorne são e salvo.</t>
+          <t>Oh... seu acampamento não fica longe daqui?
+Então irei até lá e esperarei suas notícias. Procure-me quando terminar sua busca, tenho algo que preciso lhe contar.
+Pois bem, aventureiro, desejo seu retorno são e salvo.</t>
         </is>
       </c>
     </row>
@@ -775,9 +772,8 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Vejo que você retornou são e salvo._x000D_
-_x000D_
-Deixe-me me apresentar novamente... Sou Farris, de Olvina, um contador de histórias e tecelão do antigo saber. Em troca da sua ajuda, contarei o que sei sobre Nymelle.</t>
+          <t>Vejo que voltou são e salvo.
+Deixe-me me apresentar de novo... sou Farris de Olvina, contadora de histórias e tecelã do saber antigo. Em troca da sua ajuda, contarei o que sei de Nymelle.</t>
         </is>
       </c>
     </row>
@@ -799,9 +795,8 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Nymelle... a caverna também conhecida como o cemitério dos ventos, uma das ruínas espalhadas por Tyris. Como o nome sugere, era uma caverna tranquila, onde o som do vento ecoava melancolicamente de lugar nenhum... Ou devo dizer, era... Após a Guerra dos Dez Anos, Nymelle mudou._x000D_
-_x000D_
-O som do vento cessou, as florestas ao redor de Nymelle murcharam, e estranhas criaturas começaram a vagar pela terra.</t>
+          <t>Nymelle... a caverna também conhecida como cemitério dos ventos, uma das ruínas espalhadas por Tyris. Como o nome diz, é uma caverna pacífica onde o som do vento ecoa com tristeza do nada... ou melhor, era. Depois da Guerra dos Dez Anos, Nymelle mudou.
+O som do vento cessou, as florestas ao redor de Nymelle murcharam, e monstros estranhos vieram rondar a terra.</t>
         </is>
       </c>
     </row>
@@ -823,9 +818,8 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Qual é a causa dessas anomalias... o que está acontecendo nas profundezas de Nymelle?_x000D_
-_x000D_
-Segundo a lenda, nas camadas mais profundas da caverna jazem relíquias de deuses esquecidos. Talvez tenhamos provocado a ira dos antigos-</t>
+          <t>Qual é a causa das anomalias... o que está acontecendo nas profundezas de Nymelle?
+Segundo a lenda, nas camadas mais fundas da caverna jazem as relíquias de deuses esquecidos. Quem sabe não incorremos na ira dos velhos—</t>
         </is>
       </c>
     </row>
@@ -864,9 +858,8 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-Não, não é uma relíquia sagrada que está consagrada nas profundezas de Nymelle. Nem a causa da anomalia é uma maldição divina._x000D_
-_x000D_
-Desculpe interromper, mas parece que esta caverna ainda é exatamente o que pensávamos que era...</t>
+          <t>-Não, não é uma relíquia sagrada que está consagrada no fundo de Nymelle. Nem a causa da anomalia é uma maldição de deus.
+Desculpe interromper, mas parece que esta caverna, afinal, ainda é o que pensávamos...</t>
         </is>
       </c>
     </row>
@@ -916,7 +909,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Está tudo bem, Fia. Deixe-me continuar.</t>
+          <t>Está bem, Fia. Deixa eu continuar.</t>
         </is>
       </c>
     </row>
@@ -956,11 +949,9 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>...A Guerra dos Dez Anos e a anomalia em Nymelle não são eventos desconectados._x000D_
-_x000D_
-Você provavelmente já ouviu histórias sobre a última guerra. O conflito entre o Novo Reino de Yerl e o Império do Deserto no continente oriental logo se espalhou para outras partes do mundo, mergulhando Ylva no caos._x000D_
-_x000D_
-As nações de Tyris formaram uma aliança para lutar na guerra, mas eram apenas crianças diante do império, que possuía os dirigíveis de Cyra.</t>
+          <t>...A Guerra dos Dez Anos e a anomalia em Nymelle não estão desconectadas.
+Você provavelmente ouviu histórias sobre a última guerra. A guerra que estourou entre o Novo Reino de Yerl e o Império do Deserto no continente oriental logo se espalhou por outras partes do mundo, trazendo caos a Ylva.
+As nações de Tyris formaram uma união para lutar na guerra, mas eram só bebês diante do império que possuía a aeronave de Cyra.</t>
         </is>
       </c>
     </row>
@@ -987,8 +978,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Quando nossa terra estava prestes a ser esmagada, meu Lorde Cetrus falou ao vento. Uma rajada de vento cintilante surgiu no céu de Nymelle e atingiu o império. E o dirigível de Cyra, antes considerado invencível, caiu na terra de Mysilia._x000D_
-_x000D_
+          <t>Justo quando nossa terra estava para ser pisoteada por completo, meu Lorde Cetrus falou com o vento. Uma rajada de vento cintilante apareceu no céu de Nymelle e golpeou o império. E a aeronave Cyrana, que cantavam como invencível, despencou na terra de Mysilia.
 ...Foi o fim da Guerra dos Dez Anos.</t>
         </is>
       </c>
@@ -1017,9 +1007,8 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Certamente foi o Lorde Cetrus quem invocou a "Tempestade de Nymelle". Mas será que foi apenas isso?_x000D_
-_x000D_
-O vento de luz que dançou sobre Mysilia e a estranha anomalia em Nymelle... Algo deve ter respondido à oração de Lorde Cetrus em Nymelle, na caverna conhecida como o cemitério dos ventos. Suspeito que o mistério esteja oculto nas profundezas de Nymelle.</t>
+          <t>Certamente deve ter sido o Lorde Cetrus quem invocou a "Tempestade de Nymelle". Mas será que era só isso?
+O vento de luz que dançou sobre Mysilia e a estranha anomalia em Nymelle. Algo deve ter respondido à prece do Lorde Cetrus em Nymelle, na caverna chamada cemitério dos ventos. Palpito que o mistério se esconde no fundo de Nymelle.</t>
         </is>
       </c>
     </row>
@@ -1048,11 +1037,9 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Nuvens escuras voltam a pairar sobre Tyris._x000D_
-_x000D_
-O império afiou suas garras quebradas, e é apenas uma questão de tempo até que reconstruam sua frota de dirigíveis Cyran. Desta vez, atacarão sem piedade para se vingar._x000D_
-_x000D_
-Lorde Cetrus ainda espera pela reconciliação entre humanos e eleas, mas isso será em vão se Mysilia for destruída. Precisamos obter o "poder" que repousa em Nymelle para sobreviver.</t>
+          <t>Nuvens negras pairam de novo sobre Tyris.
+O império afiou suas garras quebradas e é questão de tempo até reerguer a frota de aeronaves Cyranas. Dessa vez, atacarão sem piedade para extrair sua vingança.
+O Lorde Cetrus ainda espera a reunião de humanos e eleas, mas de nada valerá se Mysilia for destruída. Precisamos obter o "poder" que jaz em Nymelle para sobreviver.</t>
         </is>
       </c>
     </row>
@@ -1081,11 +1068,9 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Não podemos lhe contar tudo, nem sabemos de tudo ainda. Sim, você deve estar pensando que se meteu em uma grande encrenca._x000D_
-_x000D_
-Mas agora que se estabeleceu aqui e se tornou parte de Tyris, isso também lhe diz respeito._x000D_
-_x000D_
-Bem, é melhor aceitar e cooperar com nossa investigação. Quem sabe, talvez haja um ou dois tesouros nas profundezas da caverna.</t>
+          <t>Não podemos contar tudo, nem sabemos tudo ainda. Sim, você deve estar pensando que se meteu numa encrenca.
+Mas agora que você se estabeleceu aqui e virou parte de Tyris, também não lhe é indiferente.
+Bom, você vai ter de se render e cooperar com nossa investigação. Quem sabe, talvez haja um tesouro ou outro no fundo da caverna.</t>
         </is>
       </c>
     </row>
@@ -1131,9 +1116,8 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>...Sim, eu ouvi a história._x000D_
-_x000D_
-Também é meu dever descobrir a causa da anomalia em Nymelle.</t>
+          <t>...Sim, ouvi a história.
+Também é meu dever conhecer a causa da anomalia em Nymelle.</t>
         </is>
       </c>
     </row>
@@ -1155,8 +1139,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Permanecerei aqui para ver o desfecho disso._x000D_
-_x000D_
+          <t>Ficarei aqui para ver o fim disto.
 Desejo-lhe boa sorte, aventureiro. E que o vento abençoe seu caminho.</t>
         </is>
       </c>
@@ -1327,7 +1310,7 @@
       </c>
       <c r="K74" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sussurrando)  </t>
+          <t xml:space="preserve">(sussurrando) </t>
         </is>
       </c>
       <c r="L74" s="16" t="n"/>
@@ -1353,7 +1336,7 @@
       </c>
       <c r="K75" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sussurrando)  </t>
+          <t xml:space="preserve">(sussurrando) </t>
         </is>
       </c>
       <c r="L75" s="16" t="n"/>
@@ -1374,7 +1357,7 @@
       </c>
       <c r="K76" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">De fato... (sussurrando)  </t>
+          <t>De fato... (sussurrando)</t>
         </is>
       </c>
       <c r="L76" s="16" t="n"/>
@@ -1400,7 +1383,7 @@
       </c>
       <c r="K77" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sussurrando)  </t>
+          <t xml:space="preserve">(sussurrando) </t>
         </is>
       </c>
       <c r="L77" s="16" t="n"/>
@@ -1421,7 +1404,7 @@
       </c>
       <c r="K78" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh, céus...! (sussurrando)  </t>
+          <t>Ai, meu...! (sussurrando)</t>
         </is>
       </c>
       <c r="L78" s="16" t="n"/>
@@ -1447,7 +1430,7 @@
       </c>
       <c r="K79" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olá, Lady Farris.  </t>
+          <t xml:space="preserve">Olá, Lady Farris. </t>
         </is>
       </c>
       <c r="L79" s="16" t="n"/>
@@ -1468,7 +1451,7 @@
       </c>
       <c r="K80" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh, Lord Loytel. Estávamos justamente falando sobre você.  </t>
+          <t>Oh, Lorde Loytel. Estávamos justamente falando de você.</t>
         </is>
       </c>
       <c r="L80" s="16" t="n"/>
@@ -1494,7 +1477,7 @@
       </c>
       <c r="K81" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  </t>
+          <t xml:space="preserve">... </t>
         </is>
       </c>
       <c r="L81" s="16" t="n"/>
@@ -1520,7 +1503,7 @@
       </c>
       <c r="K82" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">E... eek.!  </t>
+          <t>E...eek.!</t>
         </is>
       </c>
       <c r="L82" s="16" t="n"/>
@@ -1546,7 +1529,7 @@
       </c>
       <c r="K83" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...!  </t>
+          <t>...!</t>
         </is>
       </c>
       <c r="L83" s="16" t="n"/>
@@ -1572,7 +1555,7 @@
       </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ah, oh... um, Quruitzia, para onde você está indo... espere!  </t>
+          <t xml:space="preserve">Ah, oh... hum, Quruitzia, para onde você vai... espera! </t>
         </is>
       </c>
       <c r="L84" s="16" t="n"/>
@@ -1594,7 +1577,7 @@
       </c>
       <c r="K85" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  </t>
+          <t xml:space="preserve">... </t>
         </is>
       </c>
       <c r="L85" s="16" t="n"/>
@@ -1620,7 +1603,7 @@
       </c>
       <c r="K86" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  </t>
+          <t xml:space="preserve">... </t>
         </is>
       </c>
       <c r="L86" s="16" t="n"/>
@@ -1641,7 +1624,7 @@
       </c>
       <c r="K87" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lord Loytel, dizer "Eek!" ao ver uma jovem garota...  </t>
+          <t xml:space="preserve">Lorde Loytel, soltar um "Eek!" ao ver uma jovem moça... </t>
         </is>
       </c>
       <c r="L87" s="16" t="n"/>
@@ -1669,9 +1652,8 @@
       </c>
       <c r="K88" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não, não foi isso que eu quis dizer!  _x000D_
-_x000D_
-Mas... me lembrei da história sobre os olhos dela. Você já ouviu isso do Kettle, não ouviu? Acho que ela não gosta de mim... Posso simplesmente cair morto um dia...  </t>
+          <t>Não, não foi minha intenção!
+Mas... lembrei da história dos olhos dela. Você ouviu do Kettle, não ouviu? Acho que ela gosta pouco de mim... Posso simplesmente cair morto um dia desses...</t>
         </is>
       </c>
       <c r="L88" s="16" t="n"/>
@@ -1692,7 +1674,7 @@
       </c>
       <c r="K89" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lord Loytel, estou desapontada com você.  </t>
+          <t>Lorde Loytel, estou decepcionada com o senhor.</t>
         </is>
       </c>
       <c r="L89" s="16" t="n"/>
@@ -1713,7 +1695,7 @@
       </c>
       <c r="K90" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temê-la como uma “maldição” sem nem ao menos entender seus poderes... Não percebe que essa atitude é o que mais a machuca?  </t>
+          <t>Temer ela como uma "maldição" sem nem entender seus poderes... Não vê que uma atitude assim é o que mais machuca ela?</t>
         </is>
       </c>
       <c r="L90" s="16" t="n"/>
@@ -1739,7 +1721,7 @@
       </c>
       <c r="K91" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mas...  </t>
+          <t>Mas...</t>
         </is>
       </c>
       <c r="L91" s="16" t="n"/>
@@ -1760,7 +1742,7 @@
       </c>
       <c r="K92" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nada de "mas"! Antes de temer a “maldição”, deveria considerar o quanto de solidão ela enfrentou. Não importa a cor dos olhos ou o passado dela, ela é apenas uma garota. Ela tem um coração, Lord Loytel.  </t>
+          <t>Não há mas! Antes de temer a "maldição", devia pensar em quanta solidão ela já enfrentou. Não importa a cor dos olhos nem o passado: ela é só uma garota. Ela tem coração, Lorde Loytel.</t>
         </is>
       </c>
       <c r="L92" s="16" t="n"/>
@@ -1788,9 +1770,8 @@
       </c>
       <c r="K93" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lady Farris... Você está certa.  _x000D_
-_x000D_
-Para falar a verdade, eu também quero me dar bem com ela. Mas é como se falássemos línguas diferentes, ou algo assim...  </t>
+          <t>Lady Farris... Você tem razão.
+Para dizer a verdade, eu também queria me dar bem com ela. Mas é como se não falássemos a mesma língua, sei lá...</t>
         </is>
       </c>
       <c r="L93" s="16" t="n"/>
@@ -1818,7 +1799,7 @@
       </c>
       <c r="K95" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quruitzia é uma garota delicada e reservada. Talvez você esteja se contendo demais por medo de machucá-la, tornando tudo ainda mais estranho.  </t>
+          <t>Quruitzia é uma garota delicada e quieta. Talvez você esteja se segurando demais com medo de magoá-la, e isso deixa tudo esquisito.</t>
         </is>
       </c>
       <c r="L95" s="16" t="n"/>
@@ -1841,9 +1822,8 @@
       </c>
       <c r="K96" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Existem gramáticas e boas maneiras nas histórias. Os heróis das histórias superam conflitos ferozes para desenvolver uma confiança verdadeira.  _x000D_
-_x000D_
-Você entende, Lord Loytel? Sim, se deseja abrir o coração dela, precisa confrontá-la de verdade e despertar seus sentimentos genuínos. Deve abraçar os gritos da alma dela, expostos sob a luz do dia, com toda a sua força!  </t>
+          <t>...Há gramáticas e boas maneiras nas histórias. Os heróis das histórias superam conflitos ferozes para criar confiança de verdade.
+Entende, Lorde Loytel? Sim, se quer abrir o coração dela, tem de esbarrar nela de corpo inteiro e arrancar os sentimentos verdadeiros dela. Tem de acolher com todas as forças os gritos da alma dela expostos à luz do dia!</t>
         </is>
       </c>
       <c r="L96" s="16" t="n"/>
@@ -1871,9 +1851,8 @@
       </c>
       <c r="K97" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uh... bem, isso soa um pouco dramático, mas entendo o que você quer dizer, Lady Farris.  _x000D_
-_x000D_
-Despertar os sentimentos verdadeiros de Quruitzia... Céus, isso será um desafio.   </t>
+          <t xml:space="preserve">Uh... bom, parece um pouco dramático, mas entendi o que você quer dizer, Lady Farris.
+Arrancar os sentimentos verdadeiros de Quruitzia... Meus bons, será um desafio. </t>
         </is>
       </c>
       <c r="L97" s="16" t="n"/>
@@ -2040,9 +2019,8 @@
       </c>
       <c r="K109" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">#pc, você chegou na hora perfeita.  _x000D_
-_x000D_
-Sim... estávamos confrontando Lord Loytel, que não dá sinais de pagar sua dívida.  </t>
+          <t>#pc, chegou na hora perfeita.
+Sim... estávamos confrontando o Lorde Loytel, que não mostra sinais de pagar a dívida.</t>
         </is>
       </c>
       <c r="L109" s="16" t="n"/>
@@ -2064,7 +2042,7 @@
       </c>
       <c r="K110" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lord Loytel... agora, mostre-nos seu grande plano para quitar a dívida!  </t>
+          <t>Lorde Loytel... agora, mostre a nós seu grande plano para pagar a dívida!</t>
         </is>
       </c>
       <c r="L110" s="16" t="n"/>
@@ -2090,7 +2068,7 @@
       </c>
       <c r="K111" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  </t>
+          <t>...</t>
         </is>
       </c>
       <c r="L111" s="16" t="n"/>
@@ -2118,9 +2096,8 @@
       </c>
       <c r="K112" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não existe plano, Lady Farris...  _x000D_
-_x000D_
-Como eu deveria pagar uma quantia absurda de vinte milhões de orens!? Eu... eu...!  </t>
+          <t>Não há plano, Lady Farris...
+Como pago um valor ridículo desses, vinte milhões de orens! Eu... eu...!</t>
         </is>
       </c>
       <c r="L112" s="16" t="n"/>
@@ -2162,7 +2139,7 @@
       </c>
       <c r="K114" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ah! Lorde Loytel!?  </t>
+          <t>Ah! Lorde Loytel!?</t>
         </is>
       </c>
       <c r="L114" s="16" t="n"/>
@@ -2184,7 +2161,7 @@
       </c>
       <c r="K115" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Todos, Lorde Loytel fugiu...! Rápido, rápido, peguem-no! Olhe, Kettle, você também, vá atrás dele!  </t>
+          <t>Todos, o Lorde Loytel fugiu...! Rápido, rápido, peguem ele! Olha, Kettle, você também, vá atrás!</t>
         </is>
       </c>
       <c r="L115" s="16" t="n"/>
@@ -2210,7 +2187,7 @@
       </c>
       <c r="K116" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">O-o-okay...  </t>
+          <t>O-ok...</t>
         </is>
       </c>
       <c r="L116" s="16" t="n"/>
@@ -2236,7 +2213,7 @@
       </c>
       <c r="K117" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huff, huff, droga... Eu não vou ser pego!  </t>
+          <t>Huf, huf, que raiva...não serei pego!</t>
         </is>
       </c>
       <c r="L117" s="16" t="n"/>
@@ -2262,7 +2239,7 @@
       </c>
       <c r="K118" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hah, com a força que desenvolvi desbravando terras, não tem como eu ser capturado por algumas crianças e mulheres....  </t>
+          <t>Hah, com a força que construí no pioneirismo, não há jeito de ser pego por umas crianças e mulheres....</t>
         </is>
       </c>
       <c r="L118" s="16" t="n"/>
@@ -2317,7 +2294,7 @@
       </c>
       <c r="K121" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mookyuu!  </t>
+          <t>Mookyuu!</t>
         </is>
       </c>
       <c r="L121" s="16" t="n"/>
@@ -2355,7 +2332,7 @@
       </c>
       <c r="K123" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Gah!  </t>
+          <t>...Gah!</t>
         </is>
       </c>
       <c r="L123" s="16" t="n"/>
@@ -2381,7 +2358,7 @@
       </c>
       <c r="K124" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom garoto, Corgon, continue segurando o Loytel!  </t>
+          <t>Isso, Corgon, continua segurando o Loytel!</t>
         </is>
       </c>
       <c r="L124" s="16" t="n"/>
@@ -2407,7 +2384,7 @@
       </c>
       <c r="K125" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huff... huff...  </t>
+          <t>Huf... huf...</t>
         </is>
       </c>
       <c r="L125" s="16" t="n"/>
@@ -2434,7 +2411,7 @@
       </c>
       <c r="K126" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agora, desista, Loytel.  </t>
+          <t>Agora, renda-se, Loytel.</t>
         </is>
       </c>
       <c r="L126" s="16" t="n"/>
@@ -2460,7 +2437,7 @@
       </c>
       <c r="K127" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vocês... se juntando contra mim...  </t>
+          <t>Vocês...vindo todos pra cima de mim...</t>
         </is>
       </c>
       <c r="L127" s="16" t="n"/>
@@ -2489,9 +2466,8 @@
       </c>
       <c r="K128" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Certo, certo, eu tenho um plano de pagamento meio acabado!  _x000D_
-_x000D_
-Vou buscá-lo... apenas esperem aqui por um momento.  </t>
+          <t>Tá bom, tá bom, eu tenho um plano de pagamento pela metade!
+Vou buscar... só esperem aqui um instante.</t>
         </is>
       </c>
       <c r="L128" s="16" t="n"/>
@@ -2518,7 +2494,7 @@
       </c>
       <c r="K129" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...  </t>
+          <t>...</t>
         </is>
       </c>
       <c r="L129" s="16" t="n"/>
@@ -2557,7 +2533,7 @@
       </c>
       <c r="K131" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ah! Lord Loytel!  </t>
+          <t>Ah! Lorde Loytel!</t>
         </is>
       </c>
       <c r="L131" s="16" t="n"/>
@@ -2614,7 +2590,7 @@
       </c>
       <c r="K135" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Ele fugiu... não foi?  </t>
+          <t xml:space="preserve">...Ele fugiu...não fugiu? </t>
         </is>
       </c>
       <c r="L135" s="16" t="n"/>
@@ -2636,7 +2612,7 @@
       </c>
       <c r="K136" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conhecendo Lord Loytel, não acho que ele faria algo drástico em desespero, mas...  </t>
+          <t>Conhecendo o Lorde Loytel, não acho que ele fará nada drástico em desespero, mas...</t>
         </is>
       </c>
       <c r="L136" s="16" t="n"/>
@@ -2659,7 +2635,7 @@
       </c>
       <c r="K137" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ainda assim, estou preocupada. #pc, se tiver alguma ideia de onde Lord Loytel possa ter ido, poderia procurá-lo, por favor?  </t>
+          <t>Ainda assim, estou preocupada. #pc, se você tiver qualquer ideia de para onde o Lorde Loytel possa ter fugido, poderia ir procurá-lo, por favor?</t>
         </is>
       </c>
       <c r="L137" s="16" t="n"/>
@@ -2775,7 +2751,7 @@
       </c>
       <c r="K148" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(sussurrando)  </t>
+          <t xml:space="preserve">(sussurrando) </t>
         </is>
       </c>
       <c r="L148" s="16" t="n"/>
@@ -2801,7 +2777,7 @@
       </c>
       <c r="K149" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hmmm... (sussurrando)  </t>
+          <t xml:space="preserve">Hmmm... (sussurrando) </t>
         </is>
       </c>
       <c r="L149" s="16" t="n"/>
@@ -2822,7 +2798,7 @@
       </c>
       <c r="K150" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Então, veja bem... (sussurrando)  </t>
+          <t>Então, entende... (sussurrando)</t>
         </is>
       </c>
       <c r="L150" s="16" t="n"/>
@@ -2850,7 +2826,7 @@
       </c>
       <c r="K151" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minha nossa, sério...  </t>
+          <t>Meus bons, de verdade...</t>
         </is>
       </c>
       <c r="L151" s="16" t="n"/>
@@ -2878,9 +2854,8 @@
       </c>
       <c r="K152" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desde que aquele Demitas apareceu, o ambiente tem estado pesado. Quruitzia voltou a se isolar também.  _x000D_
-_x000D_
-Ele só fica soltando palavras que semeiam a ansiedade... um homem bastante problemático.  </t>
+          <t>Desde que aquele Demitas apareceu, a atmosfera anda pesada. A Quruitzia ficou recolhida de novo também.
+Ele vive soltando palavras que mexem com a ansiedade... um homem bem chato.</t>
         </is>
       </c>
       <c r="L152" s="16" t="n"/>
@@ -2902,7 +2877,7 @@
       </c>
       <c r="K153" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mas Lord Loytel, não acredito que ele seja realmente uma má pessoa. Acho que Demitas tem um coração doente.  </t>
+          <t>Mas o Lorde Loytel, não acredito que ele seja de verdade uma pessoa má. Acho que o Demitas está doente por dentro.</t>
         </is>
       </c>
       <c r="L153" s="16" t="n"/>
@@ -2928,7 +2903,7 @@
       </c>
       <c r="K154" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hmm, um coração doente?  </t>
+          <t xml:space="preserve">Hum, doente por dentro? </t>
         </is>
       </c>
       <c r="L154" s="16" t="n"/>
@@ -2951,9 +2926,8 @@
       </c>
       <c r="K155" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não posso afirmar com certeza. Mas há algo profundamente distorcido dentro de Demitas...  _x000D_
-_x000D_
-Por trás daquela aparência sinistra e modo de falar, me pergunto quanta dor e tristeza ele carrega. Ele é uma pessoa muito intrigante.  </t>
+          <t xml:space="preserve">Não posso afirmar. Mas há algo bem torto dentro de Demitas...
+Por trás daquela aparência e jeito de falar sinistros, pergunto-me quanta dor e tristeza ele carrega. É uma pessoa bem intrigante. </t>
         </is>
       </c>
       <c r="L155" s="16" t="n"/>
@@ -2981,9 +2955,8 @@
       </c>
       <c r="K156" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Agora que menciona, Lady Farris, seus olhos sempre parecem brilhar quando olha para Demitas.  _x000D_
-_x000D_
-Bem, ele é um sujeito assustador, mas não parece ser puramente maligno.  </t>
+          <t>...Agora que comentou, Lady Farris, seus olhos sempre parecem brilhar quando olha para o Demitas.
+Bom, ele é um homem assustador, mas não passa a impressão de ser puramente maligno.</t>
         </is>
       </c>
       <c r="L156" s="16" t="n"/>
@@ -3006,9 +2979,8 @@
       </c>
       <c r="K157" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demitas, o Exilado... me pergunto como ele era antes de se tornar...  _x000D_
-_x000D_
-E o que o levou ao exílio, afinal? Um dia, adoraria ouvir essa história dele mesmo.  </t>
+          <t>Demitas, o Exilado... como seria ele antes de virar...
+E o que o fez ser exilado, para começo de conversa? Um dia, adoraria ouvir a história por ele mesmo.</t>
         </is>
       </c>
       <c r="L157" s="16" t="n"/>
